--- a/downld08.xlsx
+++ b/downld08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH363"/>
+  <dimension ref="A1:AH365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46056,6 +46056,258 @@
         <v>30</v>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" s="3" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C364" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D364" s="4" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="E364" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="F364" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="G364" s="4" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="H364" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I364" s="3" t="inlineStr">
+        <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="J364" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K364" s="4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L364" s="3" t="inlineStr">
+        <is>
+          <t>NNE</t>
+        </is>
+      </c>
+      <c r="M364" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="N364" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="O364" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="P364" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q364" s="4" t="n">
+        <v>1006.3</v>
+      </c>
+      <c r="R364" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S364" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T364" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U364" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V364" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W364" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X364" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y364" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z364" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA364" s="4" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="AB364" s="4" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="AC364" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD364" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE364" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF364" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG364" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH364" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="6" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B365" s="6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C365" s="7" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="D365" s="7" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="E365" s="7" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F365" s="8" t="n">
+        <v>48</v>
+      </c>
+      <c r="G365" s="7" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H365" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I365" s="6" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="J365" s="7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K365" s="7" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="L365" s="6" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="M365" s="7" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="N365" s="7" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="O365" s="7" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="P365" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q365" s="7" t="n">
+        <v>1005.2</v>
+      </c>
+      <c r="R365" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S365" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T365" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U365" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V365" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W365" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X365" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y365" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z365" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA365" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AB365" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="AC365" s="8" t="n">
+        <v>57</v>
+      </c>
+      <c r="AD365" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE365" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF365" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG365" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH365" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>

--- a/downld08.xlsx
+++ b/downld08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH365"/>
+  <dimension ref="A1:AH366"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46308,6 +46308,132 @@
         <v>30</v>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C366" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D366" s="4" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="E366" s="4" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="F366" s="5" t="n">
+        <v>48</v>
+      </c>
+      <c r="G366" s="4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H366" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I366" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="J366" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K366" s="4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L366" s="3" t="inlineStr">
+        <is>
+          <t>ENE</t>
+        </is>
+      </c>
+      <c r="M366" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="N366" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="O366" s="4" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="P366" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q366" s="4" t="n">
+        <v>1004.1</v>
+      </c>
+      <c r="R366" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S366" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T366" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U366" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V366" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W366" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X366" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y366" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z366" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA366" s="4" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="AB366" s="4" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="AC366" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD366" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE366" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF366" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG366" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH366" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>

--- a/downld08.xlsx
+++ b/downld08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH366"/>
+  <dimension ref="A1:AH368"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -46434,6 +46434,258 @@
         <v>30</v>
       </c>
     </row>
+    <row r="367">
+      <c r="A367" s="6" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B367" s="6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C367" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="D367" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="E367" s="7" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="F367" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="G367" s="7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="H367" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I367" s="6" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="J367" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K367" s="7" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="L367" s="6" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="M367" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="N367" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="O367" s="7" t="n">
+        <v>29</v>
+      </c>
+      <c r="P367" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q367" s="7" t="n">
+        <v>1003.1</v>
+      </c>
+      <c r="R367" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S367" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T367" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U367" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V367" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W367" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X367" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y367" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z367" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA367" s="7" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="AB367" s="7" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="AC367" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD367" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE367" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF367" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG367" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH367" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>10/09/26</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C368" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="D368" s="4" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="E368" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="F368" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="G368" s="4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="H368" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I368" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="J368" s="4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="K368" s="4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="L368" s="3" t="inlineStr">
+        <is>
+          <t>NE</t>
+        </is>
+      </c>
+      <c r="M368" s="4" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="N368" s="4" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="O368" s="4" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="P368" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q368" s="4" t="n">
+        <v>1002.5</v>
+      </c>
+      <c r="R368" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S368" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T368" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U368" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V368" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W368" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X368" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y368" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z368" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA368" s="4" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="AB368" s="4" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="AC368" s="5" t="n">
+        <v>61</v>
+      </c>
+      <c r="AD368" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE368" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF368" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG368" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH368" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>

--- a/downld08.xlsx
+++ b/downld08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH357"/>
+  <dimension ref="A1:AH360"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -45300,6 +45300,384 @@
         <v>30</v>
       </c>
     </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="inlineStr">
+        <is>
+          <t>9:30</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D358" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="E358" s="4" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="F358" s="5" t="n">
+        <v>77</v>
+      </c>
+      <c r="G358" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I358" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K358" s="4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L358" s="3" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="M358" s="4" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="N358" s="4" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="O358" s="4" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="P358" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q358" s="4" t="n">
+        <v>1006.4</v>
+      </c>
+      <c r="R358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T358" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U358" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V358" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W358" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X358" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y358" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA358" s="4" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="AB358" s="4" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AC358" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD358" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE358" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF358" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG358" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH358" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="6" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B359" s="6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C359" s="7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="D359" s="7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E359" s="7" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="F359" s="8" t="n">
+        <v>70</v>
+      </c>
+      <c r="G359" s="7" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H359" s="7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I359" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J359" s="7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K359" s="7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L359" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="M359" s="7" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="N359" s="7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="O359" s="7" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="P359" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q359" s="7" t="n">
+        <v>1007</v>
+      </c>
+      <c r="R359" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S359" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T359" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U359" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V359" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W359" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X359" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y359" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z359" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA359" s="7" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="AB359" s="7" t="n">
+        <v>24.1</v>
+      </c>
+      <c r="AC359" s="8" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD359" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE359" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF359" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG359" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH359" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="D360" s="4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E360" s="4" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="F360" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="G360" s="4" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H360" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I360" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J360" s="4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K360" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L360" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="M360" s="4" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="N360" s="4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="O360" s="4" t="n">
+        <v>22.7</v>
+      </c>
+      <c r="P360" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q360" s="4" t="n">
+        <v>1007.8</v>
+      </c>
+      <c r="R360" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S360" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T360" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U360" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V360" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W360" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X360" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y360" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z360" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA360" s="4" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AB360" s="4" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AC360" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD360" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE360" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF360" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG360" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH360" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>

--- a/downld08.xlsx
+++ b/downld08.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH360"/>
+  <dimension ref="A1:AH363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -45678,6 +45678,384 @@
         <v>30</v>
       </c>
     </row>
+    <row r="361">
+      <c r="A361" s="6" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B361" s="6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="C361" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="D361" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="E361" s="7" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="F361" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="G361" s="7" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H361" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I361" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J361" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K361" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L361" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="M361" s="7" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N361" s="7" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="O361" s="7" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="P361" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q361" s="7" t="n">
+        <v>1008.1</v>
+      </c>
+      <c r="R361" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S361" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T361" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U361" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V361" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W361" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X361" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y361" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z361" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA361" s="7" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AB361" s="7" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="AC361" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD361" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE361" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF361" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG361" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH361" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="3" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C362" s="4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="D362" s="4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="E362" s="4" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F362" s="5" t="n">
+        <v>56</v>
+      </c>
+      <c r="G362" s="4" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="H362" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I362" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J362" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K362" s="4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L362" s="3" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="M362" s="4" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="N362" s="4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="O362" s="4" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="P362" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q362" s="4" t="n">
+        <v>1008.2</v>
+      </c>
+      <c r="R362" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S362" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T362" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U362" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V362" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W362" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X362" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y362" s="3" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z362" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA362" s="4" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="AB362" s="4" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AC362" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AD362" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE362" s="5" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF362" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG362" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH362" s="5" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="6" t="inlineStr">
+        <is>
+          <t>11/09/26</t>
+        </is>
+      </c>
+      <c r="B363" s="6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C363" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D363" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="E363" s="7" t="n">
+        <v>24.7</v>
+      </c>
+      <c r="F363" s="8" t="n">
+        <v>53</v>
+      </c>
+      <c r="G363" s="7" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="H363" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I363" s="6" t="inlineStr">
+        <is>
+          <t>ESE</t>
+        </is>
+      </c>
+      <c r="J363" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K363" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="L363" s="6" t="inlineStr">
+        <is>
+          <t>WSW</t>
+        </is>
+      </c>
+      <c r="M363" s="7" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="N363" s="7" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="O363" s="7" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="P363" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Q363" s="7" t="n">
+        <v>1007.9</v>
+      </c>
+      <c r="R363" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S363" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T363" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="U363" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="V363" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="W363" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="X363" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Y363" s="6" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+      <c r="Z363" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA363" s="7" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="AB363" s="7" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="AC363" s="8" t="n">
+        <v>58</v>
+      </c>
+      <c r="AD363" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE363" s="8" t="n">
+        <v>640</v>
+      </c>
+      <c r="AF363" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG363" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AH363" s="8" t="n">
+        <v>30</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:AH1"/>
